--- a/docs/design/ACSMS-SCR-008/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_管理支店マスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-008/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_管理支店マスタ明細検索画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1990,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2151,7 +2151,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2268,7 +2268,7 @@
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
@@ -2279,7 +2279,7 @@
       <c r="I6" s="11" t="n"/>
       <c r="J6" s="19" t="inlineStr">
         <is>
-          <t>UNAUTHORIZED</t>
+          <t>BAD_REQUEST</t>
         </is>
       </c>
       <c r="K6" s="10" t="n"/>
@@ -2295,7 +2295,7 @@
       <c r="U6" s="11" t="n"/>
       <c r="V6" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください。</t>
+          <t>リクエストパラメータが不正です。</t>
         </is>
       </c>
       <c r="W6" s="10" t="n"/>
@@ -2321,7 +2321,7 @@
       <c r="B7" s="11" t="n"/>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D7" s="10" t="n"/>
@@ -2332,7 +2332,7 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>FORBIDDEN</t>
+          <t>UNAUTHORIZED</t>
         </is>
       </c>
       <c r="K7" s="10" t="n"/>
@@ -2348,7 +2348,7 @@
       <c r="U7" s="11" t="n"/>
       <c r="V7" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません。</t>
+          <t>セッションが切れました。再度ログインしてください。</t>
         </is>
       </c>
       <c r="W7" s="10" t="n"/>
@@ -2374,7 +2374,7 @@
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D8" s="10" t="n"/>
@@ -2385,7 +2385,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>BAD_REQUEST</t>
+          <t>FORBIDDEN</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -2401,7 +2401,7 @@
       <c r="U8" s="11" t="n"/>
       <c r="V8" s="19" t="inlineStr">
         <is>
-          <t>リクエストパラメータが不正です。</t>
+          <t>この画面へのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W8" s="10" t="n"/>
@@ -2427,7 +2427,7 @@
       <c r="B9" s="11" t="n"/>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>VALIDATION_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D9" s="10" t="n"/>
@@ -2438,7 +2438,7 @@
       <c r="I9" s="11" t="n"/>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>VALIDATION_ERROR</t>
+          <t>DATA_SCOPE_VIOLATION</t>
         </is>
       </c>
       <c r="K9" s="10" t="n"/>
@@ -2454,7 +2454,7 @@
       <c r="U9" s="11" t="n"/>
       <c r="V9" s="19" t="inlineStr">
         <is>
-          <t>入力値が不正です。詳細はerrorsフィールドを確認してください。</t>
+          <t>このデータへのアクセス権限がありません。</t>
         </is>
       </c>
       <c r="W9" s="10" t="n"/>
@@ -2480,7 +2480,7 @@
       <c r="B10" s="11" t="n"/>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -2491,7 +2491,7 @@
       <c r="I10" s="11" t="n"/>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>NOT_FOUND</t>
+          <t>VALIDATION_ERROR</t>
         </is>
       </c>
       <c r="K10" s="10" t="n"/>
@@ -2507,7 +2507,7 @@
       <c r="U10" s="11" t="n"/>
       <c r="V10" s="19" t="inlineStr">
         <is>
-          <t>指定された管理支店が見つかりません。</t>
+          <t>入力値が不正です。詳細はerrorsフィールドを確認してください。</t>
         </is>
       </c>
       <c r="W10" s="10" t="n"/>
@@ -2533,7 +2533,7 @@
       <c r="B11" s="11" t="n"/>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D11" s="10" t="n"/>
@@ -2544,7 +2544,7 @@
       <c r="I11" s="11" t="n"/>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>TOO_MANY_REQUESTS</t>
         </is>
       </c>
       <c r="K11" s="10" t="n"/>
@@ -2560,7 +2560,7 @@
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>リクエスト回数が上限を超えました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
       <c r="W11" s="10" t="n"/>
@@ -2586,7 +2586,7 @@
       <c r="B12" s="11" t="n"/>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>INTERNAL_SERVER_ERROR</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -2632,8 +2632,114 @@
       <c r="AJ12" s="10" t="n"/>
       <c r="AK12" s="11" t="n"/>
     </row>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="A13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="19" t="inlineStr">
+        <is>
+          <t>指定された管理支店が見つかりません。</t>
+        </is>
+      </c>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="10" t="n"/>
+      <c r="Z13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n"/>
+      <c r="AB13" s="10" t="n"/>
+      <c r="AC13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n"/>
+      <c r="AE13" s="10" t="n"/>
+      <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>画面固有</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>CONFLICT</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="19" t="inlineStr">
+        <is>
+          <t>関連データが存在するため処理を実行できません。</t>
+        </is>
+      </c>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="10" t="n"/>
+      <c r="Z14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n"/>
+      <c r="AB14" s="10" t="n"/>
+      <c r="AC14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n"/>
+      <c r="AE14" s="10" t="n"/>
+      <c r="AF14" s="10" t="n"/>
+      <c r="AG14" s="10" t="n"/>
+      <c r="AH14" s="10" t="n"/>
+      <c r="AI14" s="10" t="n"/>
+      <c r="AJ14" s="10" t="n"/>
+      <c r="AK14" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="54">
     <mergeCell ref="V11:AK11"/>
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
@@ -2644,6 +2750,7 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="V7:AK7"/>
     <mergeCell ref="J11:U11"/>
+    <mergeCell ref="C13:I13"/>
     <mergeCell ref="J7:U7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="Q2:U3"/>
@@ -2655,11 +2762,15 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C14:I14"/>
     <mergeCell ref="J12:U12"/>
     <mergeCell ref="V5:AK5"/>
     <mergeCell ref="V8:AK8"/>
+    <mergeCell ref="V14:AK14"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="V13:AK13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="C10:I10"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J8:U8"/>
@@ -2671,11 +2782,14 @@
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="J5:U5"/>
     <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J14:U14"/>
     <mergeCell ref="J10:U10"/>
     <mergeCell ref="V9:AK9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C12:I12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="J13:U13"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="V6:AK6"/>
     <mergeCell ref="C11:I11"/>
@@ -2852,7 +2966,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3126,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3287,7 +3401,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4082,13 +4196,13 @@
       <c r="AJ24" s="10" t="n"/>
       <c r="AK24" s="11" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="B25" s="31" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -4129,13 +4243,13 @@
       <c r="AA25" s="10" t="n"/>
       <c r="AB25" s="11" t="n"/>
       <c r="AC25" s="17" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>電話番号（部分一致）</t>
+          <t>都道府県コード（完全一致。画面ではプルダウン選択／m_todofuken.todofuken_codeを参照）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -4150,7 +4264,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -4197,7 +4311,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>FAX番号（部分一致）</t>
+          <t>電話番号（部分一致）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -4212,7 +4326,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -4226,7 +4340,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
@@ -4252,12 +4366,14 @@
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="11" t="n"/>
-      <c r="AC27" s="17" t="inlineStr"/>
+      <c r="AC27" s="17" t="n">
+        <v>15</v>
+      </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>FAX番号（部分一致）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -4272,7 +4388,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4317,7 +4433,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数（デフォルト: 20）</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4326,13 +4442,13 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="54" customHeight="1">
+    <row r="29" ht="18" customHeight="1">
       <c r="B29" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -4346,7 +4462,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -4377,7 +4493,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（m_kanri_shitenテーブルのカラム名を指定。例: kanri_shiten_code, kanri_shiten_name, yubin_no, todofuken_name, tel, fax, paper_flg, denshi_flg）</t>
+          <t>1ページの件数（デフォルト: 20）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -4386,13 +4502,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="54" customHeight="1">
       <c r="B30" s="31" t="n">
         <v>8</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -4437,7 +4553,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>ソート方向（asc / desc）</t>
+          <t>ソート項目（kanri_shiten_code, kanri_shiten_name, todofuken_code, updated_at のいずれか。画面定義§8.1の3項目に加え、初期表示用に updated_at を許可）</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -4446,88 +4562,84 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="17" t="inlineStr"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="17" t="inlineStr"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="19" t="inlineStr">
+        <is>
+          <t>ソート方向（asc / desc）</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1"/>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1"/>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="B34" s="30" t="inlineStr">
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -4539,29 +4651,33 @@
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R35" s="10" t="n"/>
       <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
       <c r="W35" s="10" t="n"/>
       <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -4570,9 +4686,9 @@
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>管理支店一覧データ</t>
+      <c r="AF35" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4583,14 +4699,14 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="37" t="n"/>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -4601,7 +4717,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -4609,7 +4725,7 @@
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
@@ -4632,7 +4748,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>管理支店一覧データ</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4643,12 +4759,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C37" s="37" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_code</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4661,7 +4777,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4692,7 +4808,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>管理支店コード</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4703,12 +4819,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4721,7 +4837,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -4752,7 +4868,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>管理支店名</t>
+          <t>JA ID（DataScope判定用）</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4763,12 +4879,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4801,7 +4917,7 @@
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z39" s="10" t="n"/>
@@ -4812,7 +4928,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>JA名（m_jaからJOIN）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4823,12 +4939,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>kanri_shiten_code</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4861,7 +4977,7 @@
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z40" s="10" t="n"/>
@@ -4872,7 +4988,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>管理支店コード</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -4883,12 +4999,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -4921,7 +5037,7 @@
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z41" s="10" t="n"/>
@@ -4932,7 +5048,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>都道府県名（m_todofukenからJOIN）</t>
+          <t>管理支店名</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -4943,12 +5059,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -4981,7 +5097,7 @@
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z42" s="10" t="n"/>
@@ -4992,7 +5108,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5003,12 +5119,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5041,7 +5157,7 @@
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z43" s="10" t="n"/>
@@ -5052,7 +5168,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5063,12 +5179,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5101,7 +5217,7 @@
       <c r="X44" s="11" t="n"/>
       <c r="Y44" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z44" s="10" t="n"/>
@@ -5112,7 +5228,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>都道府県名（m_todofukenからJOIN）</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5123,12 +5239,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5141,7 +5257,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -5172,7 +5288,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5183,12 +5299,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="C46" s="39" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5201,7 +5317,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -5232,7 +5348,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5243,14 +5359,14 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>fax</t>
+        </is>
+      </c>
       <c r="E47" s="10" t="n"/>
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
@@ -5261,7 +5377,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -5292,7 +5408,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>ページング情報</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5303,12 +5419,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="C48" s="37" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5321,7 +5437,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5352,7 +5468,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5363,12 +5479,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="38" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="C49" s="39" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5381,7 +5497,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N49" s="10" t="n"/>
@@ -5412,7 +5528,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5423,14 +5539,14 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
@@ -5441,7 +5557,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5472,7 +5588,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>1ページの件数</t>
+          <t>ページング情報</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5483,12 +5599,12 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="39" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C51" s="37" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5532,7 +5648,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5541,21 +5657,136 @@
       <c r="AJ51" s="10" t="n"/>
       <c r="AK51" s="11" t="n"/>
     </row>
-    <row r="52" ht="19.5" customHeight="1"/>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="B53" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="17" t="inlineStr"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="11" t="n"/>
+      <c r="Y52" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="11" t="n"/>
+      <c r="AF52" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="B53" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="17" t="inlineStr"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="11" t="n"/>
+      <c r="Y53" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" s="10" t="n"/>
+      <c r="AA53" s="10" t="n"/>
+      <c r="AB53" s="10" t="n"/>
+      <c r="AC53" s="10" t="n"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="11" t="n"/>
+      <c r="AF53" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="11" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/kanri-shiten?kanri_shiten_code=3300&amp;kanri_shiten_name=北海道&amp;page=1&amp;per_page=20&amp;sort_by=kanri_shiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n"/>
+      <c r="B54" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
@@ -5563,79 +5794,61 @@
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="10" t="n"/>
       <c r="K54" s="10" t="n"/>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="n"/>
-      <c r="P54" s="10" t="n"/>
-      <c r="Q54" s="10" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R54" s="10" t="n"/>
-      <c r="S54" s="10" t="n"/>
-      <c r="T54" s="10" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="17" t="inlineStr"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
-      <c r="X54" s="10" t="n"/>
-      <c r="Y54" s="10" t="n"/>
+      <c r="X54" s="11" t="n"/>
+      <c r="Y54" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z54" s="10" t="n"/>
       <c r="AA54" s="10" t="n"/>
       <c r="AB54" s="10" t="n"/>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="10" t="n"/>
-      <c r="AF54" s="10" t="n"/>
+      <c r="AE54" s="11" t="n"/>
+      <c r="AF54" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
       <c r="AG54" s="10" t="n"/>
       <c r="AH54" s="10" t="n"/>
       <c r="AI54" s="10" t="n"/>
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
+    <row r="55" ht="19.5" customHeight="1"/>
     <row r="56" ht="19.5" customHeight="1">
       <c r="B56" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="409" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
       <c r="C57" s="19" t="inlineStr">
         <is>
-          <t>{
-  "data": [
-    {
-      "kanri_shiten_id": 1,
-      "kanri_shiten_code": "013-3300-001",
-      "kanri_shiten_name": "JA北海道中央管理支店",
-      "yubin_no": "060-0001",
-      "todofuken_code": "01",
-      "todofuken_name": "北海道",
-      "address": "札幌市中央区北1条西2丁目",
-      "tel": "011-222-3333",
-      "fax": "011-222-3334",
-      "paper_flg": true,
-      "denshi_flg": true
-    },
-    {
-      "kanri_shiten_id": 2,
-      "kanri_shiten_code": "013-3300-002",
-      "kanri_shiten_name": "JA北海道東部管理支店",
-      "yubin_no": "085-0017",
-      "todofuken_code": "01",
-      "todofuken_name": "北海道",
-      "address": "釧路市幸町10-1",
-      "tel": "0154-41-5678",
-      "fax": "0154-41-5679",
-      "paper_flg": true,
-      "denshi_flg": false
-    }
-  ],
-  "meta": {
-    "total": 15,
-    "page": 1,
-    "per_page": 20,
-    "total_pages": 1
-  }
-}</t>
+          <t>GET /api/v1/kanri-shiten?kanri_shiten_code=3300&amp;kanri_shiten_name=北海道&amp;todofuken_code=01&amp;page=1&amp;per_page=20&amp;sort_by=kanri_shiten_code&amp;sort_order=asc</t>
         </is>
       </c>
       <c r="D57" s="10" t="n"/>
@@ -5676,16 +5889,52 @@
     <row r="59" ht="19.5" customHeight="1">
       <c r="B59" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 400 Bad Request）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="72" customHeight="1">
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="409" customHeight="1">
       <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "BAD_REQUEST",
-  "message": "リクエストパラメータが不正です"
+  "data": [
+    {
+      "kanri_shiten_id": 1,
+      "ja_id": 1,
+      "ja_name": "JA北海道",
+      "kanri_shiten_code": "013-3300-001",
+      "kanri_shiten_name": "JA北海道中央管理支店",
+      "yubin_no": "060-0001",
+      "todofuken_code": "01",
+      "todofuken_name": "北海道",
+      "address": "札幌市中央区北1条西2丁目",
+      "tel": "011-222-3333",
+      "fax": "011-222-3334",
+      "paper_flg": true,
+      "denshi_flg": true
+    },
+    {
+      "kanri_shiten_id": 2,
+      "ja_id": 1,
+      "ja_name": "JA北海道",
+      "kanri_shiten_code": "013-3300-002",
+      "kanri_shiten_name": "JA北海道東部管理支店",
+      "yubin_no": "085-0017",
+      "todofuken_code": "01",
+      "todofuken_name": "北海道",
+      "address": "釧路市幸町10-1",
+      "tel": "0154-41-5678",
+      "fax": "0154-41-5679",
+      "paper_flg": true,
+      "denshi_flg": false
+    }
+  ],
+  "meta": {
+    "total": 15,
+    "page": 1,
+    "per_page": 20,
+    "total_pages": 1
+  }
 }</t>
         </is>
       </c>
@@ -5727,7 +5976,7 @@
     <row r="62" ht="19.5" customHeight="1">
       <c r="B62" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
+          <t>レスポンス（失敗 400 Bad Request）</t>
         </is>
       </c>
     </row>
@@ -5735,8 +5984,8 @@
       <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "error_code": "BAD_REQUEST",
+  "message": "リクエストパラメータが不正です"
 }</t>
         </is>
       </c>
@@ -5778,7 +6027,7 @@
     <row r="65" ht="19.5" customHeight="1">
       <c r="B65" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -5786,8 +6035,8 @@
       <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
 }</t>
         </is>
       </c>
@@ -5829,7 +6078,7 @@
     <row r="68" ht="19.5" customHeight="1">
       <c r="B68" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -5837,8 +6086,8 @@
       <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
 }</t>
         </is>
       </c>
@@ -5877,320 +6126,408 @@
       <c r="AJ69" s="10" t="n"/>
       <c r="AK69" s="11" t="n"/>
     </row>
-    <row r="71" ht="19.5" customHeight="1"/>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1"/>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_code：文字列型、最大15文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_name：文字列型、最大100文字</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>tel：文字列型、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>fax：文字列型、最大15文字</t>
+          <t>kanri_shiten_code：文字列型、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>page：数値型、1以上の整数</t>
+          <t>kanri_shiten_name：文字列型、最大100文字</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>per_page：数値型、1以上100以下の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
+          <t>todofuken_code：文字列型、最大2文字（数字。プルダウン由来）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
-          <t>sort_by：列挙型（kanri_shiten_code, kanri_shiten_name, yubin_no, todofuken_name, tel, fax, paper_flg, denshi_flg）</t>
+          <t>tel：文字列型、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>sort_order：列挙型（asc, desc）</t>
+          <t>fax：文字列型、最大15文字</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>デフォルト値の適用：</t>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>page：数値型、1以上の整数</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>page：未指定の場合、1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
+          <t>per_page：数値型、1以上100以下の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="54" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>per_page：未指定の場合、20</t>
+          <t>sort_by：列挙型（kanri_shiten_code, kanri_shiten_name, todofuken_code, updated_at）※画面定義§8.1の3項目 + 初期表示用 updated_at</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>sort_by：未指定の場合、kanri_shiten_code</t>
+          <t>sort_order：列挙型（asc, desc）</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="D87" s="41" t="inlineStr">
-        <is>
-          <t>sort_order：未指定の場合、asc</t>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>デフォルト値の適用：</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D88" s="41" t="inlineStr">
+        <is>
+          <t>page：未指定の場合、1</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="B90" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+          <t>per_page：未指定の場合、20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：未指定の場合、updated_at（直近に登録・更新したレコードを先頭に表示するため）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：未指定の場合、desc</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：kanri-shiten.view を保持しているか確認する。</t>
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）</t>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="C95" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
-      <c r="B96" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="C97" s="41" t="inlineStr">
         <is>
+          <t>権限チェック：kanri_shiten.view を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden（ACSMS-MSG-008-002）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>データスコープの適用：</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="D99" s="41" t="inlineStr">
-        <is>
-          <t>NICHINO_ADMIN：全JA管理支店レコードを取得（ja_idフィルタなし）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>基本条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="D101" s="41" t="inlineStr">
-        <is>
-          <t>論理削除除外（deleted_at IS NULL）</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>検索条件：</t>
+          <t>データスコープの適用（画面定義§1.3）：</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="D103" s="41" t="inlineStr">
         <is>
-          <t>kanri_shiten_code：部分一致（ILIKE '%value%'）</t>
+          <t>NICHINO_ADMIN：全JA管理支店レコードを取得（ja_idフィルタなし）</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="D104" s="41" t="inlineStr">
         <is>
-          <t>kanri_shiten_name：部分一致（ILIKE '%value%'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
+          <t>CHUOKAI：自中央会配下の管理支店レコードのみ（自JAの`ja_id`に一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
       <c r="D105" s="41" t="inlineStr">
         <is>
-          <t>tel：部分一致（ILIKE '%value%'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
+          <t>JA_HONTEN：自JAの管理支店レコードのみ（`mks.ja_id = session.ja_id`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="54" customHeight="1">
       <c r="D106" s="41" t="inlineStr">
         <is>
-          <t>fax：部分一致（ILIKE '%value%'）</t>
+          <t>JA_KANRI_SHITEN：自管理支店のレコードのみ（`mks.kanri_shiten_id = session.kanri_shiten_id`。kanri_shiten_id はJAをまたいで一意なため、ja_id条件は付与しない）</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>sort_by / sort_order：ソート適用</t>
+      <c r="C107" s="41" t="inlineStr">
+        <is>
+          <t>基本条件：</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="B108" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ件数の取得</t>
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>論理削除除外（deleted_at IS NULL）</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="C109" s="41" t="inlineStr">
         <is>
+          <t>検索条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_code：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_name：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code：完全一致（= 'value'）※プルダウン選択（仕様§2.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>tel：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="D114" s="41" t="inlineStr">
+        <is>
+          <t>fax：部分一致（ILIKE '%value%'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="D115" s="41" t="inlineStr">
+        <is>
+          <t>sort_by / sort_order：ソート適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ件数の取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="C117" s="41" t="inlineStr">
+        <is>
           <t>条件に一致する総件数を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
         <is>
           <t>meta.total に使用する。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="27" t="inlineStr">
         <is>
           <t>4.5 ソート・ページング</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="C120" s="41" t="inlineStr">
         <is>
           <t>sort_by / sort_order でソート適用。</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="C121" s="41" t="inlineStr">
         <is>
           <t>OFFSET = (page - 1) \* per_page, LIMIT = per_page</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="B122" s="27" t="inlineStr">
         <is>
           <t>4.6 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行してデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="396" customHeight="1">
-      <c r="C116" s="42" t="inlineStr">
+    <row r="124" ht="409" customHeight="1">
+      <c r="C124" s="42" t="inlineStr">
         <is>
           <t>SELECT
     mks.kanri_shiten_id,
+    mks.ja_id,
+    mj.ja_name,
     mks.kanri_shiten_code,
     mks.kanri_shiten_name,
     mks.yubin_no,
@@ -6203,88 +6540,131 @@
     mks.denshi_flg
 FROM m_kanri_shiten mks
 LEFT JOIN m_todofuken mt ON mks.todofuken_code = mt.todofuken_code
+LEFT JOIN m_ja mj ON mks.ja_id = mj.ja_id
 WHERE mks.deleted_at IS NULL
   AND (:kanri_shiten_code IS NULL OR mks.kanri_shiten_code ILIKE '%' || :kanri_shiten_code || '%')
   AND (:kanri_shiten_name IS NULL OR mks.kanri_shiten_name ILIKE '%' || :kanri_shiten_name || '%')
+  AND (:todofuken_code IS NULL OR mks.todofuken_code = :todofuken_code)
   AND (:tel IS NULL OR mks.tel ILIKE '%' || :tel || '%')
   AND (:fax IS NULL OR mks.fax ILIKE '%' || :fax || '%')
-ORDER BY {sort_by} {sort_order}
+  -- DataScope (§4.3): role に応じて追加される条件
+  AND (
+    :role IN ('NICHINO_ADMIN', 'NICHINO_STAFF')
+    OR (:role IN ('CHUOKAI', 'JA_HONTEN') AND mks.ja_id = :session_ja_id)
+    OR (:role = 'JA_KANRI_SHITEN' AND mks.kanri_shiten_id = :session_kanri_shiten_id)
+  )
+ORDER BY {sort_by} {sort_order}, mks.kanri_shiten_id DESC
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="10" t="n"/>
-      <c r="F116" s="10" t="n"/>
-      <c r="G116" s="10" t="n"/>
-      <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
-      <c r="J116" s="10" t="n"/>
-      <c r="K116" s="10" t="n"/>
-      <c r="L116" s="10" t="n"/>
-      <c r="M116" s="10" t="n"/>
-      <c r="N116" s="10" t="n"/>
-      <c r="O116" s="10" t="n"/>
-      <c r="P116" s="10" t="n"/>
-      <c r="Q116" s="10" t="n"/>
-      <c r="R116" s="10" t="n"/>
-      <c r="S116" s="10" t="n"/>
-      <c r="T116" s="10" t="n"/>
-      <c r="U116" s="10" t="n"/>
-      <c r="V116" s="10" t="n"/>
-      <c r="W116" s="10" t="n"/>
-      <c r="X116" s="10" t="n"/>
-      <c r="Y116" s="10" t="n"/>
-      <c r="Z116" s="10" t="n"/>
-      <c r="AA116" s="10" t="n"/>
-      <c r="AB116" s="10" t="n"/>
-      <c r="AC116" s="10" t="n"/>
-      <c r="AD116" s="10" t="n"/>
-      <c r="AE116" s="10" t="n"/>
-      <c r="AF116" s="10" t="n"/>
-      <c r="AG116" s="10" t="n"/>
-      <c r="AH116" s="10" t="n"/>
-      <c r="AI116" s="10" t="n"/>
-      <c r="AJ116" s="10" t="n"/>
-      <c r="AK116" s="11" t="n"/>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="C117" s="41" t="inlineStr">
-        <is>
-          <t>NICHINO_ADMIN は全JA横断で管理支店を取得するため、ja_idフィルタは適用しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="B118" s="27" t="inlineStr">
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="10" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="10" t="n"/>
+      <c r="K124" s="10" t="n"/>
+      <c r="L124" s="10" t="n"/>
+      <c r="M124" s="10" t="n"/>
+      <c r="N124" s="10" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="10" t="n"/>
+      <c r="R124" s="10" t="n"/>
+      <c r="S124" s="10" t="n"/>
+      <c r="T124" s="10" t="n"/>
+      <c r="U124" s="10" t="n"/>
+      <c r="V124" s="10" t="n"/>
+      <c r="W124" s="10" t="n"/>
+      <c r="X124" s="10" t="n"/>
+      <c r="Y124" s="10" t="n"/>
+      <c r="Z124" s="10" t="n"/>
+      <c r="AA124" s="10" t="n"/>
+      <c r="AB124" s="10" t="n"/>
+      <c r="AC124" s="10" t="n"/>
+      <c r="AD124" s="10" t="n"/>
+      <c r="AE124" s="10" t="n"/>
+      <c r="AF124" s="10" t="n"/>
+      <c r="AG124" s="10" t="n"/>
+      <c r="AH124" s="10" t="n"/>
+      <c r="AI124" s="10" t="n"/>
+      <c r="AJ124" s="10" t="n"/>
+      <c r="AK124" s="11" t="n"/>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="C125" s="41" t="inlineStr">
+        <is>
+          <t>実装上は上記 SQL 相当だが、todofuken_name / ja_name は行毎 JOIN でなく、</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="C126" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_ADMIN / NICHINO_STAFF は全JA横断で管理支店を取得するため、ja_idフィルタを適用しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="C127" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI / JA_HONTEN は自JAの管理支店のみ取得する（`mks.ja_id = session.ja_id`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="C128" s="41" t="inlineStr">
+        <is>
+          <t>JA_KANRI_SHITEN は自管理支店のレコードのみ取得する（`mks.kanri_shiten_id = session.kanri_shiten_id`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="C129" s="41" t="inlineStr">
+        <is>
+          <t>同一ソートキーの行を決定的な順序で返すため、ORDER BY に kanri_shiten_id DESC のタイブレーカを追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="36" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
+        <is>
+          <t>検索結果がない場合は、UI側で ACSMS-MSG-008-001 を表示する（API は空配列＋total=0 を返す）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="B131" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="C132" s="41" t="inlineStr">
         <is>
           <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="B133" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="C121" s="41" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="C134" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 Internal Server Error を返却する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="277">
+  <mergeCells count="306">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -6299,13 +6679,15 @@
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D78:AK78"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="D87:AK87"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="T53:X53"/>
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
@@ -6313,43 +6695,43 @@
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
-    <mergeCell ref="B73:AK73"/>
+    <mergeCell ref="D113:AK113"/>
+    <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
-    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="C109:AK109"/>
+    <mergeCell ref="D115:AK115"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C51:C54"/>
     <mergeCell ref="D106:AK106"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="D99:AK99"/>
+    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C37:C49"/>
     <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="D101:AK101"/>
     <mergeCell ref="B68:I68"/>
-    <mergeCell ref="B114:AK114"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="D77:AK77"/>
-    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
@@ -6357,30 +6739,37 @@
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D75:AK75"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="D103:AK103"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="A32:AK32"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="D114:AK114"/>
     <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="B119:AK119"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
-    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="T54:X54"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="B116:AK116"/>
+    <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="D98:AK98"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -6393,10 +6782,11 @@
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="D79:AK79"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B118:AK118"/>
+    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
@@ -6404,49 +6794,57 @@
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="D90:AK90"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="C48:C51"/>
+    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D76:AK76"/>
-    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B90:AK90"/>
+    <mergeCell ref="A75:AK75"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="D52:L52"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
+    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="C125:AK125"/>
+    <mergeCell ref="B131:AK131"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="M53:P53"/>
     <mergeCell ref="A20:AK20"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="A72:AK72"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -6455,27 +6853,24 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="C54:AK54"/>
-    <mergeCell ref="B108:AK108"/>
+    <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="C63:AK63"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="C121:AK121"/>
+    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
@@ -6485,26 +6880,34 @@
     <mergeCell ref="D80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="B94:AK94"/>
+    <mergeCell ref="B133:AK133"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="M31:P31"/>
     <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
-    <mergeCell ref="C119:AK119"/>
+    <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="D46:L46"/>
+    <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B96:AK96"/>
+    <mergeCell ref="A33:AK33"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
@@ -6513,49 +6916,55 @@
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="B111:AK111"/>
-    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D43:L43"/>
+    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="C36:C46"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D85:AK85"/>
     <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
-    <mergeCell ref="D50:L50"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="C47:L47"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="B76:AK76"/>
+    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="D108:AK108"/>
+    <mergeCell ref="C31:L31"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="D86:AK86"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="C132:AK132"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="B100:AK100"/>
     <mergeCell ref="D104:AK104"/>
-    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
     <mergeCell ref="M28:P28"/>
@@ -6573,7 +6982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK94"/>
+  <dimension ref="A1:AK95"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6734,7 +7143,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7137,7 +7546,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常に削除しました</t>
+          <t>削除しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -7327,7 +7736,7 @@
       <c r="M19" s="11" t="n"/>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません</t>
+          <t>関連データが存在するため処理を実行できません</t>
         </is>
       </c>
       <c r="O19" s="10" t="n"/>
@@ -7483,7 +7892,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -7528,7 +7937,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>削除対象の kanri_shiten_id</t>
+          <t>削除対象の kanri_shiten_id（パスパラメータ）</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -7732,7 +8141,7 @@
       <c r="C36" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -7987,7 +8396,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "関連データが存在するため削除できません"
+  "message": "関連データが存在するため処理を実行できません"
 }</t>
         </is>
       </c>
@@ -8085,59 +8494,96 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
+    <row r="58" ht="54" customHeight="1">
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="C60" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="D60" s="41" t="inlineStr">
-        <is>
-          <t>id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="D61" s="41" t="inlineStr">
         <is>
-          <t>id：必須チェック</t>
+          <t>kanri_shiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="C62" s="41" t="inlineStr">
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id：必須チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="D63" s="41" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="D64" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
+    <row r="65" ht="18" customHeight="1">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
@@ -8151,225 +8597,232 @@
     <row r="67" ht="18" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：kanri-shiten.delete を保持しているか確認する。</t>
+          <t>権限チェック：kanri_shiten.delete を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="D68" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden</t>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="36" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>画面定義§1.3「管理支店マスタは日農は管理者のみ操作可」より、CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN は削除不可</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden（ACSMS-MSG-008-002）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>対象レコードの検索：</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="D72" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id = {id}</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
+          <t>kanri_shiten_id = :kanri_shiten_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="D74" s="41" t="inlineStr">
+        <is>
           <t>論理削除除外（deleted_at IS NULL）</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>対象レコードが存在しない場合：</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="D76" s="41" t="inlineStr">
         <is>
           <t>HTTP 404 Not Found を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="B76" s="27" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>4.4 関連データの存在チェック</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>以下のテーブルに関連レコードが存在するか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="198" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
+    <row r="79" ht="198" customHeight="1">
+      <c r="C79" s="42" t="inlineStr">
         <is>
           <t>-- 支店の存在チェック
 SELECT COUNT(*) FROM m_shiten
-WHERE kanri_shiten_id = :id AND deleted_at IS NULL;
+WHERE kanri_shiten_id = :kanri_shiten_id AND deleted_at IS NULL;
 -- 購読者の存在チェック
 SELECT COUNT(*) FROM t_dokusya
-WHERE kanri_shiten_id = :id AND deleted_at IS NULL;
+WHERE kanri_shiten_id = :kanri_shiten_id AND deleted_at IS NULL;
 -- アカウントの存在チェック
 SELECT COUNT(*) FROM m_account
-WHERE kanri_shiten_id = :id AND deleted_at IS NULL;</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+WHERE kanri_shiten_id = :kanri_shiten_id AND deleted_at IS NULL;</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>いずれかに関連レコードが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="D81" s="41" t="inlineStr">
         <is>
           <t>HTTP 409 Conflict を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して論理削除を行う。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="90" customHeight="1">
-      <c r="C83" s="42" t="inlineStr">
+    <row r="84" ht="90" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_kanri_shiten
 SET deleted_at = NOW(),
     updated_by = :user_account_id
-WHERE kanri_shiten_id = :id
+WHERE kanri_shiten_id = :kanri_shiten_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>削除前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
+          <t>削除前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="216" customHeight="1">
-      <c r="C87" s="42" t="inlineStr">
+    <row r="88" ht="216" customHeight="1">
+      <c r="C88" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8383,61 +8836,6 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="10" t="n"/>
-      <c r="F87" s="10" t="n"/>
-      <c r="G87" s="10" t="n"/>
-      <c r="H87" s="10" t="n"/>
-      <c r="I87" s="10" t="n"/>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="10" t="n"/>
-      <c r="M87" s="10" t="n"/>
-      <c r="N87" s="10" t="n"/>
-      <c r="O87" s="10" t="n"/>
-      <c r="P87" s="10" t="n"/>
-      <c r="Q87" s="10" t="n"/>
-      <c r="R87" s="10" t="n"/>
-      <c r="S87" s="10" t="n"/>
-      <c r="T87" s="10" t="n"/>
-      <c r="U87" s="10" t="n"/>
-      <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
-      <c r="X87" s="10" t="n"/>
-      <c r="Y87" s="10" t="n"/>
-      <c r="Z87" s="10" t="n"/>
-      <c r="AA87" s="10" t="n"/>
-      <c r="AB87" s="10" t="n"/>
-      <c r="AC87" s="10" t="n"/>
-      <c r="AD87" s="10" t="n"/>
-      <c r="AE87" s="10" t="n"/>
-      <c r="AF87" s="10" t="n"/>
-      <c r="AG87" s="10" t="n"/>
-      <c r="AH87" s="10" t="n"/>
-      <c r="AI87" s="10" t="n"/>
-      <c r="AJ87" s="10" t="n"/>
-      <c r="AK87" s="11" t="n"/>
-    </row>
-    <row r="88" ht="288" customHeight="1">
-      <c r="C88" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "kanri_shiten_id": 5,
-  "kanri_shiten_code": "013-3300-005",
-  "kanri_shiten_name": "JA削除対象管理支店",
-  "yubin_no": "060-0001",
-  "todofuken_code": "01",
-  "todofuken_name": "北海道",
-  "address": "札幌市中央区",
-  "tel": "011-333-3333",
-  "fax": "011-333-3334",
-  "paper_flg": true,
-  "denshi_flg": false
-}</t>
         </is>
       </c>
       <c r="D88" s="10" t="n"/>
@@ -8475,43 +8873,98 @@
       <c r="AJ88" s="10" t="n"/>
       <c r="AK88" s="11" t="n"/>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="B89" s="27" t="inlineStr">
+    <row r="89" ht="288" customHeight="1">
+      <c r="C89" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "kanri_shiten_id": 5,
+  "kanri_shiten_code": "013-3300-005",
+  "kanri_shiten_name": "JA削除対象管理支店",
+  "yubin_no": "060-0001",
+  "todofuken_code": "01",
+  "todofuken_name": "北海道",
+  "address": "札幌市中央区",
+  "tel": "011-333-3333",
+  "fax": "011-333-3334",
+  "paper_flg": true,
+  "denshi_flg": false
+}</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="10" t="n"/>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="10" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="10" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="10" t="n"/>
+      <c r="X89" s="10" t="n"/>
+      <c r="Y89" s="10" t="n"/>
+      <c r="Z89" s="10" t="n"/>
+      <c r="AA89" s="10" t="n"/>
+      <c r="AB89" s="10" t="n"/>
+      <c r="AC89" s="10" t="n"/>
+      <c r="AD89" s="10" t="n"/>
+      <c r="AE89" s="10" t="n"/>
+      <c r="AF89" s="10" t="n"/>
+      <c r="AG89" s="10" t="n"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="10" t="n"/>
+      <c r="AJ89" s="10" t="n"/>
+      <c r="AK89" s="11" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="C91" s="41" t="inlineStr">
         <is>
           <t>成功メッセージを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="C93" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="216" customHeight="1">
-      <c r="C94" s="42" t="inlineStr">
+    <row r="95" ht="216" customHeight="1">
+      <c r="C95" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8527,53 +8980,53 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="10" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="10" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="10" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="10" t="n"/>
+      <c r="X95" s="10" t="n"/>
+      <c r="Y95" s="10" t="n"/>
+      <c r="Z95" s="10" t="n"/>
+      <c r="AA95" s="10" t="n"/>
+      <c r="AB95" s="10" t="n"/>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="10" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="126">
+  <mergeCells count="127">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D73:AK73"/>
@@ -8581,60 +9034,62 @@
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="B65:AK65"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C51:AK51"/>
+    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="M25:P25"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="C48:AK48"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D61:AK61"/>
-    <mergeCell ref="D75:AK75"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="B47:I47"/>
     <mergeCell ref="A57:AK57"/>
-    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C33:AK33"/>
     <mergeCell ref="C42:AK42"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
-    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B14:I20"/>
-    <mergeCell ref="B89:AK89"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="J20:M20"/>
+    <mergeCell ref="D76:AK76"/>
     <mergeCell ref="C39:AK39"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B90:AK90"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="B50:I50"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="B71:AK71"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
@@ -8642,22 +9097,21 @@
     <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="C62:AK62"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C54:AK54"/>
-    <mergeCell ref="B84:AK84"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
@@ -8670,25 +9124,25 @@
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="M24:P24"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="A22:AK22"/>
+    <mergeCell ref="D74:AK74"/>
     <mergeCell ref="D68:AK68"/>
     <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D60:AK60"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="B53:I53"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="B76:AK76"/>
-    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="M30:P30"/>
+    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
